--- a/data/trans_dic/P37A$medicoenfermedad-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P37A$medicoenfermedad-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,6</t>
+          <t>0,17; 1,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,68</t>
+          <t>0,2; 1,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,67</t>
+          <t>0,21; 2,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,33</t>
+          <t>0,23; 2,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,44</t>
+          <t>0,25; 2,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,59</t>
+          <t>0,3; 5,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,23</t>
+          <t>0,26; 1,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,54</t>
+          <t>0,34; 1,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,16</t>
+          <t>0,38; 2,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,72</t>
+          <t>0,3; 3,85</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,88</t>
+          <t>0,41; 1,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,23</t>
+          <t>0,88; 3,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,08</t>
+          <t>0,34; 2,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,04</t>
+          <t>0,24; 2,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,77</t>
+          <t>0,26; 1,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,56</t>
+          <t>0,16; 1,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,19</t>
+          <t>0,34; 1,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,21</t>
+          <t>1,04; 3,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,5</t>
+          <t>0,5; 1,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,97</t>
+          <t>0,75; 2,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,64</t>
+          <t>0,5; 1,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,31</t>
+          <t>0,71; 2,38</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,39</t>
+          <t>0,34; 2,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,52</t>
+          <t>0,59; 2,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,66</t>
+          <t>0,29; 1,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,61</t>
+          <t>0,84; 3,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,7</t>
+          <t>0,84; 2,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,59</t>
+          <t>1,37; 3,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,77</t>
+          <t>0,86; 2,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,73</t>
+          <t>1,82; 4,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,13</t>
+          <t>0,77; 2,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,75</t>
+          <t>1,21; 2,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,89</t>
+          <t>0,69; 1,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,1</t>
+          <t>1,46; 3,01</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,59</t>
+          <t>1,05; 3,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,76</t>
+          <t>1,71; 4,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,72</t>
+          <t>1,71; 4,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,8</t>
+          <t>3,61; 6,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,99</t>
+          <t>1,21; 3,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,79</t>
+          <t>1,68; 4,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,31</t>
+          <t>1,6; 4,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,08</t>
+          <t>3,91; 6,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,29</t>
+          <t>1,47; 3,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,2</t>
+          <t>2,06; 4,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,88</t>
+          <t>1,96; 3,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,37</t>
+          <t>4,0; 6,02</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,84</t>
+          <t>4,63; 10,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,79</t>
+          <t>4,81; 9,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,63</t>
+          <t>5,66; 10,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 12,8</t>
+          <t>8,67; 13,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 8,36</t>
+          <t>3,61; 8,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 10,16</t>
+          <t>5,09; 9,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,87</t>
+          <t>2,75; 6,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,85</t>
+          <t>7,63; 11,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,96</t>
+          <t>4,7; 7,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,99</t>
+          <t>5,54; 8,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,12</t>
+          <t>4,67; 7,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,13</t>
+          <t>8,66; 11,6</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 14,07</t>
+          <t>7,34; 14,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,28</t>
+          <t>5,19; 12,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,07</t>
+          <t>5,6; 11,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,83</t>
+          <t>7,61; 12,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,49; 10,97</t>
+          <t>5,59; 11,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,0; 16,01</t>
+          <t>8,4; 15,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 9,26</t>
+          <t>3,98; 9,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,94</t>
+          <t>9,97; 14,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,46</t>
+          <t>7,04; 11,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 12,53</t>
+          <t>8,01; 12,62</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,61; 9,54</t>
+          <t>5,47; 9,57</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,74</t>
+          <t>9,54; 12,82</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,71; 18,33</t>
+          <t>8,59; 17,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 16,09</t>
+          <t>7,03; 15,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 10,7</t>
+          <t>4,44; 10,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,64; 15,89</t>
+          <t>9,42; 15,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,96</t>
+          <t>2,39; 7,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 9,62</t>
+          <t>4,02; 9,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,84</t>
+          <t>3,45; 8,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,13; 14,64</t>
+          <t>10,31; 14,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,76</t>
+          <t>5,47; 9,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,16; 10,89</t>
+          <t>6,33; 10,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,67</t>
+          <t>4,69; 8,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,41; 14,16</t>
+          <t>10,75; 14,47</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,1</t>
+          <t>2,86; 4,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,37</t>
+          <t>3,04; 4,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,15</t>
+          <t>2,86; 4,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,18; 6,16</t>
+          <t>4,93; 6,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,4</t>
+          <t>2,24; 3,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,68</t>
+          <t>3,27; 4,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,64</t>
+          <t>2,45; 3,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,43</t>
+          <t>5,72; 6,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,55</t>
+          <t>2,7; 3,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 4,36</t>
+          <t>3,36; 4,37</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,67</t>
+          <t>2,87; 3,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,09</t>
+          <t>5,54; 6,49</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9628</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>855; 7914</t>
+          <t>858; 7864</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>937; 7611</t>
+          <t>931; 7671</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>901; 11182</t>
+          <t>898; 11462</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 22398</t>
+          <t>0; 18178</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 8990</t>
+          <t>0; 8688</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1014; 10009</t>
+          <t>1009; 9988</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>945; 9646</t>
+          <t>1005; 9070</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>930; 17507</t>
+          <t>1079; 20019</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2521; 11785</t>
+          <t>2531; 12431</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2887; 13639</t>
+          <t>2970; 13830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3443; 17612</t>
+          <t>3127; 16429</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2475; 26513</t>
+          <t>2295; 29620</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>14050</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3069; 13835</t>
+          <t>3036; 14210</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6672; 22174</t>
+          <t>6070; 21581</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1932; 12286</t>
+          <t>1981; 12404</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1108; 8639</t>
+          <t>1143; 10219</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1822; 11081</t>
+          <t>1605; 10950</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>989; 9504</t>
+          <t>977; 9809</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2052; 12336</t>
+          <t>1938; 11127</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3710; 16445</t>
+          <t>5204; 18409</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6351; 20376</t>
+          <t>6845; 21484</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8916; 25620</t>
+          <t>9751; 26304</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5409; 18908</t>
+          <t>5750; 18502</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6171; 21659</t>
+          <t>6945; 23297</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>27302</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2916; 15292</t>
+          <t>2179; 15154</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3905; 17186</t>
+          <t>3990; 17597</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2006; 11126</t>
+          <t>1962; 11522</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4894; 19379</t>
+          <t>5197; 19151</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5902; 18628</t>
+          <t>5805; 19112</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9743; 25548</t>
+          <t>9754; 27181</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5859; 18349</t>
+          <t>5683; 19073</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9242; 22073</t>
+          <t>11337; 25058</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11053; 28270</t>
+          <t>10192; 28326</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17017; 38294</t>
+          <t>16849; 38829</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9676; 25132</t>
+          <t>9186; 24418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16871; 34938</t>
+          <t>18203; 37417</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32581</t>
+          <t>35124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65555</t>
+          <t>71796</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5190; 18637</t>
+          <t>5465; 19445</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10620; 29269</t>
+          <t>10519; 29180</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11238; 30463</t>
+          <t>11042; 28963</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13938; 51462</t>
+          <t>25307; 47839</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6201; 20570</t>
+          <t>6226; 20169</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10634; 29496</t>
+          <t>10381; 29316</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9989; 27983</t>
+          <t>10398; 26615</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24002; 43327</t>
+          <t>28777; 46969</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15216; 34001</t>
+          <t>15168; 33114</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25215; 51729</t>
+          <t>25376; 50586</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25677; 50198</t>
+          <t>25365; 49030</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38585; 85921</t>
+          <t>57509; 86542</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58873</t>
+          <t>65684</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48803</t>
+          <t>55123</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>107676</t>
+          <t>120808</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18134; 38056</t>
+          <t>17896; 38956</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20775; 42031</t>
+          <t>20673; 41525</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26243; 50796</t>
+          <t>27062; 51943</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46367; 71815</t>
+          <t>52842; 80619</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13858; 33753</t>
+          <t>14598; 32923</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22934; 45491</t>
+          <t>22781; 44034</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13721; 34120</t>
+          <t>13672; 32960</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40359; 59472</t>
+          <t>46434; 67318</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36697; 62919</t>
+          <t>37125; 62481</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49679; 78835</t>
+          <t>48607; 78394</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45377; 79117</t>
+          <t>45494; 76180</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91480; 123417</t>
+          <t>105496; 141292</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36941</t>
+          <t>40557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>47900</t>
+          <t>53390</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84841</t>
+          <t>93947</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21580; 41171</t>
+          <t>21461; 41938</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16312; 38028</t>
+          <t>16083; 38228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19661; 40348</t>
+          <t>18719; 39989</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28202; 47218</t>
+          <t>30993; 51258</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18835; 37606</t>
+          <t>19179; 38746</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31866; 56665</t>
+          <t>29719; 56277</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15975; 34975</t>
+          <t>15042; 34904</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22150; 78715</t>
+          <t>43799; 64587</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44984; 72832</t>
+          <t>44710; 72971</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51476; 83155</t>
+          <t>53180; 83785</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39977; 67942</t>
+          <t>38946; 68143</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>45183; 114681</t>
+          <t>80765; 108489</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34836</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>52029</t>
+          <t>57810</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86865</t>
+          <t>95862</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18274; 38481</t>
+          <t>18022; 37502</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18109; 40201</t>
+          <t>17563; 39176</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11618; 27506</t>
+          <t>11415; 27054</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27259; 44931</t>
+          <t>29220; 49383</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7657; 23244</t>
+          <t>7989; 23361</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16778; 37433</t>
+          <t>15636; 36207</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14672; 35376</t>
+          <t>13820; 35041</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43153; 62356</t>
+          <t>47924; 68826</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29008; 53096</t>
+          <t>29749; 53988</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39364; 69543</t>
+          <t>40464; 69384</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29700; 56986</t>
+          <t>30794; 56099</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>73776; 100370</t>
+          <t>83288; 112152</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>180994</t>
+          <t>197102</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>210781</t>
+          <t>236290</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>391775</t>
+          <t>433392</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>92818; 134187</t>
+          <t>93850; 134078</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>104290; 149818</t>
+          <t>104014; 153414</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97872; 140840</t>
+          <t>97222; 140278</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>144690; 213009</t>
+          <t>174010; 226084</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>76264; 114793</t>
+          <t>75676; 112191</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>119979; 166399</t>
+          <t>116341; 164928</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>86925; 129041</t>
+          <t>86840; 130473</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>172014; 238691</t>
+          <t>213731; 260319</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>180170; 236111</t>
+          <t>179404; 232890</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>236250; 304336</t>
+          <t>234629; 305274</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>197047; 254881</t>
+          <t>198917; 256454</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>340406; 436642</t>
+          <t>402625; 471890</t>
         </is>
       </c>
     </row>
